--- a/input_home_filtered.xlsx
+++ b/input_home_filtered.xlsx
@@ -413,9 +413,2040 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C1" t="n">
+        <v>2.624645600029241</v>
+      </c>
+      <c r="D1" t="n">
+        <v>0.4228944371259503</v>
+      </c>
+      <c r="E1" t="n">
+        <v>0.2810341347701197</v>
+      </c>
+      <c r="F1" t="n">
+        <v>4.116057044790626</v>
+      </c>
+      <c r="G1" t="n">
+        <v>0.3142191666020036</v>
+      </c>
+      <c r="H1" t="n">
+        <v>18.60151215651894</v>
+      </c>
+      <c r="I1" t="n">
+        <v>6.253301110188477</v>
+      </c>
+      <c r="J1" t="n">
+        <v>5.364750203884915</v>
+      </c>
+      <c r="K1" t="n">
+        <v>4.899029623522595</v>
+      </c>
+      <c r="L1" t="n">
+        <v>2.014822160715529</v>
+      </c>
+      <c r="M1" t="n">
+        <v>7.810663544479673</v>
+      </c>
+      <c r="N1" t="n">
+        <v>6.93776815056832</v>
+      </c>
+      <c r="O1" t="n">
+        <v>4.431571414529405</v>
+      </c>
+      <c r="P1" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T1" t="n">
+        <v>1.263740054081372</v>
+      </c>
+      <c r="U1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1" t="n">
+        <v>7.124950399672182</v>
+      </c>
+      <c r="X1" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>1.75736785659399</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>46.01476016327929</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.01738875929471901</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.001702756636837158</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.003569365467709305</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE1" t="n">
+        <v>36.12360591992946</v>
+      </c>
+      <c r="AF1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG1" t="n">
+        <v>0.005109327303276984</v>
+      </c>
+      <c r="AH1" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI1" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AJ1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AK1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AL1" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AM1" t="n">
+        <v>3.573000931818117</v>
+      </c>
+      <c r="AN1" t="n">
+        <v>1.687373891864628</v>
+      </c>
+      <c r="AO1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP1" t="n">
+        <v>7.318611302671671</v>
+      </c>
+      <c r="AQ1" t="n">
+        <v>10.9702589057802</v>
+      </c>
+      <c r="AR1" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AS1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AU1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV1" t="n">
+        <v>26.86961404004723</v>
+      </c>
+      <c r="AW1" t="n">
+        <v>33.21678618168145</v>
+      </c>
+      <c r="AX1" t="n">
+        <v>1.202319134755185</v>
+      </c>
+      <c r="AY1" t="n">
+        <v>65.16556038134323</v>
+      </c>
+      <c r="AZ1" t="n">
+        <v>44.90952109089307</v>
+      </c>
+      <c r="BA1" t="n">
+        <v>9.773739567201234</v>
+      </c>
+      <c r="BB1" t="n">
+        <v>-1.619</v>
+      </c>
+      <c r="BC1" t="n">
+        <v>8592</v>
+      </c>
+      <c r="BD1" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="BE1" t="n">
+        <v>1769.8</v>
+      </c>
+      <c r="BF1" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="BG1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="BH1" t="n">
+        <v>7.785</v>
+      </c>
+      <c r="BI1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BJ1" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BK1" t="n">
+        <v>72.47799999999999</v>
+      </c>
+      <c r="BL1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="BM1" t="n">
+        <v>22.034</v>
+      </c>
+      <c r="BN1" t="n">
+        <v>3.284</v>
+      </c>
+      <c r="BO1" t="n">
+        <v>35.752</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.85650495655575</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6808462791064019</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2511618504833931</v>
+      </c>
+      <c r="F2" t="n">
+        <v>19.40246901111095</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01090105049175251</v>
+      </c>
+      <c r="H2" t="n">
+        <v>19.35563959336351</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.436768951909658</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.87184491915933</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.17427710084455</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.03773994997315</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.690950557246325</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.599072332263632</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6.756196035316291</v>
+      </c>
+      <c r="P2" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T2" t="n">
+        <v>8.117629931541151</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>24.72759810976516</v>
+      </c>
+      <c r="X2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>27.67994256643322</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>11.14537479901405</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.2660224919712854</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.05897129168709031</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.003566727209156357</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>67.0285855464958</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.02438167935364367</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2.130257969753776</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.176174929189934</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.752394608421528</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>44.0481412728826</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>29.79411227241708</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>37.05913948851506</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>35.94172287759414</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>156.9674538360569</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>304.2870852845749</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>16.24659006067941</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-1.619</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>8592</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1769.8</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>7.785</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>72.47799999999999</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>22.034</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>3.284</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>35.752</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n">
+        <v>72.04584992142473</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2381540859288045</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.01189945937319243</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.6840551610534</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.003233636010512297</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13.90231441599097</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.139905863614229</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.758281156676661</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.838640293684266</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.19483913868564</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.084411087108841</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.73446011869645</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.390858836650517</v>
+      </c>
+      <c r="P3" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6.038934534884967</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>14.51033957738572</v>
+      </c>
+      <c r="X3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.002041691731496</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>17.12669450873294</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.003093478113085225</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.2127344662474048</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.005975387162449763</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>18.88685916176554</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.02865772374866126</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.049830118963201</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>5.677049928370925</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.358090737163947</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>37.24801365598864</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>12.27658546818892</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.146530404836336</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>10.4684860026725</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>76.10126448943824</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>10.67874889417739</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.929524390110897</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-1.619</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>8592</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1769.8</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>7.785</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>72.47799999999999</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>22.034</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>3.284</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>35.752</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5.663885870405019</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.009227019733043839</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0925875865936997</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7.57040955314132</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4173823583973701</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12.55925085155194</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.178321841652773</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.021569612662505</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.121180344975525</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.33618736378234</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.854632633441178</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.281260065090732</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.797795389039257</v>
+      </c>
+      <c r="P4" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.002066677880302</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>22.75389255227185</v>
+      </c>
+      <c r="X4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>37.60921230635203</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>57.49433090736832</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.2294704473975079</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.01192406640348045</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5144968073786407</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>14.20843610689675</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.02063748562958135</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.54992195129251</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3.730402357106044</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4.576502484691244</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>24.08990746867579</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>72.43186023054855</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.786560425283344</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.911643615410707</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10.21558666895014</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>27.22246315353338</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>7.4510253942797</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-1.619</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>8592</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1769.8</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>7.785</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>72.47799999999999</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>22.034</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>3.284</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>35.752</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C5" t="n">
+        <v>46.69718222109519</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.07420141093136294</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1353130640802513</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6.714982447612623</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.03261997875588642</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.814382941250751</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.402830730616826</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.948551504840317</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.365405211545907</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.365725652037398</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.400355754753201</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.603129291523899</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6.276711359372106</v>
+      </c>
+      <c r="P5" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.283606361057529</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.283642687648207</v>
+      </c>
+      <c r="X5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>11.24174233034105</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>44.83698397173242</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.004044198750904273</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.001031634961988427</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.102577627397502</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>10.51275898504271</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.006426047431207881</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.743298886748432</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2.231426452964624</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.080116960329074</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>24.78187691698542</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>46.14645233072311</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.783215054810987</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.427310939303219</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>123.5368337606679</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>276.3224397968215</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.92613753973206</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-1.619</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>8592</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1769.8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>7.785</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>72.47799999999999</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>22.034</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>3.284</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>35.752</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9.379756640813595</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.04900632105981607</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2758505857009971</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.049135095720916</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02590140148178926</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.906680194603794</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.614484465962155</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.712869371728964</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.226880573178217</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.117205688206125</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.458433271129259</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6.142424354023477</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.095866576101984</v>
+      </c>
+      <c r="P6" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7.270300853488886</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>99.24384993313751</v>
+      </c>
+      <c r="X6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>10.38856368522962</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>34.44222699819939</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.06710508758370076</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.5795125637606151</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.02084850806159703</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>52.9696194877612</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.08809843300322953</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.246830546567619</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>3.432397551411651</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3.31593357791691</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>54.37699568918521</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9.5807949076246</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7.33567480326589</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.12439022003546</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>24.11680706554161</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>6.021146309727622</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3.422230146706039</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-1.619</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>8592</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1769.8</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>7.785</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>72.47799999999999</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>22.034</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>3.284</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>35.752</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>24</v>
+      </c>
+      <c r="C7" t="n">
+        <v>22.26436999960995</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1599870997400225</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0512903051507248</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12.43419079427586</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.04593744862133514</v>
+      </c>
+      <c r="H7" t="n">
+        <v>13.99454945346006</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.931323401086662</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.26530018196526</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.950773292384493</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.498175194398025</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.536088413471687</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.879192369533134</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7.061239365219629</v>
+      </c>
+      <c r="P7" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.016769260860242</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>16.54422483920433</v>
+      </c>
+      <c r="X7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.387972243637805</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>51.73819204479792</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.2376568827345656</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.003083411745237574</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.140117753746788</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>56.13455789085592</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.04374823466826643</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.142461814743003</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>3.887162640672961</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.607233820496676</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>13.42913364204331</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.631317218677692</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.277731129056606</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.64641744961789</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.333956283429139</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>53.76800988043918</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>19.14487533303477</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-1.619</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>8592</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1769.8</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>7.785</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>72.47799999999999</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>22.034</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>3.284</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>35.752</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="n">
+        <v>24</v>
+      </c>
+      <c r="C8" t="n">
+        <v>56.77545300639991</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.01071170710580024</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0739490015452639</v>
+      </c>
+      <c r="F8" t="n">
+        <v>37.01906129860612</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0122894067912696</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7.230620405658603</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.756867375922956</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.913276271000146</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.82741970757138</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.388757555318234</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.999284954612539</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.429059660882014</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.752949853462382</v>
+      </c>
+      <c r="P8" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.261444933739939</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.195821387053563</v>
+      </c>
+      <c r="X8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>64.36969806645946</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>54.15416013175602</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.001692272973570823</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.003065965399039811</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.02235368091690499</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>26.65093391855495</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.6272563328767455</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.897150388623759</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>4.503010411561246</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>3.718185409093903</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>30.46188375698856</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.829865371408276</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.246609816812063</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.386246596696959</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>12.79404090775655</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>7.31176265391078</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>53.27406743927168</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-1.619</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8592</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1769.8</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>7.785</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>72.47799999999999</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>22.034</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>3.284</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>35.752</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C9" t="n">
+        <v>20.01949168566397</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1436804419289488</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2138589082388256</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14.39717970164245</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1019894429444134</v>
+      </c>
+      <c r="H9" t="n">
+        <v>48.1179589435061</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.761309244512625</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.92969787230581</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.131333689778582</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.092512392971699</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.392837476277311</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.120554839962668</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9.078529622329023</v>
+      </c>
+      <c r="P9" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.171675229446766</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7.422267056456102</v>
+      </c>
+      <c r="X9" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>80.93766884683811</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>63.35757310054579</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.02069788787165764</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.07518050746424822</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.685612615751735</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>66.15690431092681</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.0092313316697957</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.669920341738279</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.702588185887329</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.239932294418709</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11.66906657823577</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>12.54411160596529</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>11.17116906361924</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>11.13732848695389</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>18.81370721522565</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>128.6662553710724</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>12.72225937417835</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-1.619</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>8592</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1769.8</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>7.785</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>72.47799999999999</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>22.034</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>3.284</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>35.752</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.589256542102138</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.04348574000766144</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3615194732580368</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.013501058523384</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.003423970761123295</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.110597121341366</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.126955094120341</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.716000206334606</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.146310239665764</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.063124498704862</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7.121107058722164</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.685314624062074</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6.576131603937956</v>
+      </c>
+      <c r="P10" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.969737971146087</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>21.75614729232993</v>
+      </c>
+      <c r="X10" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>26.92800277386486</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>34.96175927353148</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.09645365858237577</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.007268280701694626</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.03423391087458417</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>23.21070577352978</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.007106420083834219</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>2.382250382224053</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.063733589456633</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>5.542282003599244</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13.392155232207</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.696617094738414</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>50.57839252531996</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.4932942192452344</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>145.2180167872444</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>9.775290035472889</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>154.3614975696017</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-1.619</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>8592</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1769.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>7.785</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>72.47799999999999</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>22.034</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>3.284</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>35.752</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>